--- a/output/yearly_surface_area_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_39_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497648511016</v>
+        <v>10.84497613602075</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907247466897</v>
+        <v>37.78907125827491</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.381360077604268</v>
+        <v>4.82332647096458</v>
       </c>
       <c r="C2" t="n">
-        <v>10.55378782065321</v>
+        <v>13.24770352110646</v>
       </c>
       <c r="D2" t="n">
-        <v>21.98427634119883</v>
+        <v>29.67626960397258</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.776546738526</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="C3" t="n">
-        <v>29.07445826126929</v>
+        <v>25.56471021858694</v>
       </c>
       <c r="D3" t="n">
-        <v>69.63045592370503</v>
+        <v>83.02640334815275</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.55840312620073</v>
+        <v>35.82495547567036</v>
       </c>
       <c r="C4" t="n">
-        <v>69.02079059936776</v>
+        <v>71.56057191025425</v>
       </c>
       <c r="D4" t="n">
-        <v>85.89310664455344</v>
+        <v>111.4313096751257</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.7141822160065</v>
+        <v>41.77336481570179</v>
       </c>
       <c r="C5" t="n">
-        <v>93.06968236259763</v>
+        <v>117.7606371244049</v>
       </c>
       <c r="D5" t="n">
-        <v>61.23651305239481</v>
+        <v>79.59519512181016</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.72337779824321</v>
+        <v>39.1246095096439</v>
       </c>
       <c r="C6" t="n">
-        <v>102.1184509526405</v>
+        <v>143.0141333207457</v>
       </c>
       <c r="D6" t="n">
-        <v>42.7070068824405</v>
+        <v>50.59633143376788</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.53083207502382</v>
+        <v>26.58965482182061</v>
       </c>
       <c r="C7" t="n">
-        <v>102.2863298100667</v>
+        <v>133.7866866485298</v>
       </c>
       <c r="D7" t="n">
-        <v>38.14777054391831</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.19316761802514</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>72.26644850960771</v>
+        <v>88.37201959777664</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.542186774651494</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>48.36874589283183</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.687403827580245</v>
+        <v>7.649094739076346</v>
       </c>
       <c r="C21" t="n">
-        <v>94.170696887858</v>
+        <v>92.74527371130068</v>
       </c>
       <c r="D21" t="n">
-        <v>8.648329306027776</v>
+        <v>7.649094739076346</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.59029241215959</v>
+        <v>5.874778262212914</v>
       </c>
       <c r="C2" t="n">
-        <v>9.493500300066657</v>
+        <v>17.73625402492288</v>
       </c>
       <c r="D2" t="n">
-        <v>31.03206318353743</v>
+        <v>27.9464301490897</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.97151362104362</v>
+        <v>17.18549356284042</v>
       </c>
       <c r="C3" t="n">
-        <v>35.06311925717483</v>
+        <v>38.19489443372216</v>
       </c>
       <c r="D3" t="n">
-        <v>70.43058030266617</v>
+        <v>85.94219402976579</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.98858854711009</v>
+        <v>35.32720938961722</v>
       </c>
       <c r="C4" t="n">
-        <v>70.06733365209485</v>
+        <v>67.71899314353648</v>
       </c>
       <c r="D4" t="n">
-        <v>98.80897944162447</v>
+        <v>123.0070968558999</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.89919275276141</v>
+        <v>46.60847225911733</v>
       </c>
       <c r="C5" t="n">
-        <v>109.7839370273996</v>
+        <v>122.9393562643069</v>
       </c>
       <c r="D5" t="n">
-        <v>74.73554398578845</v>
+        <v>97.85570242080085</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.55107322838128</v>
+        <v>46.53091419048183</v>
       </c>
       <c r="C6" t="n">
-        <v>122.888305383686</v>
+        <v>163.3009678813017</v>
       </c>
       <c r="D6" t="n">
-        <v>50.99884799250906</v>
+        <v>60.94100699341652</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.56804067679396</v>
+        <v>35.27321326588365</v>
       </c>
       <c r="C7" t="n">
-        <v>124.6240353247943</v>
+        <v>165.7062497567064</v>
       </c>
       <c r="D7" t="n">
-        <v>41.08221443191203</v>
+        <v>44.43586458961913</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.45595720759379</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="C8" t="n">
-        <v>101.8072369303942</v>
+        <v>127.7597374921587</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>64.78749449865549</v>
+        <v>76.10311853780424</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00131020953629</v>
+        <v>42.99073196896783</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.868140534295631</v>
+        <v>7.819397730832087</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2858269458432</v>
+        <v>100.6747457844631</v>
       </c>
       <c r="D21" t="n">
-        <v>9.835175667869539</v>
+        <v>8.796822447186097</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.171487053073703</v>
+        <v>7.616398689546754</v>
       </c>
       <c r="C2" t="n">
-        <v>14.31977201414398</v>
+        <v>17.4976893327909</v>
       </c>
       <c r="D2" t="n">
-        <v>28.74851802345935</v>
+        <v>29.856911181554</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.66150233067988</v>
+        <v>17.82853830912208</v>
       </c>
       <c r="C3" t="n">
-        <v>35.9810533606456</v>
+        <v>51.40430979436299</v>
       </c>
       <c r="D3" t="n">
-        <v>76.09035581764904</v>
+        <v>86.89448930288519</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.64024803855171</v>
+        <v>33.25964872447344</v>
       </c>
       <c r="C4" t="n">
-        <v>77.04854157699393</v>
+        <v>78.69493247701583</v>
       </c>
       <c r="D4" t="n">
-        <v>106.9898830611131</v>
+        <v>133.727781786275</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.42719309119694</v>
+        <v>48.67014243803564</v>
       </c>
       <c r="C5" t="n">
-        <v>116.9752389610075</v>
+        <v>122.1294144083032</v>
       </c>
       <c r="D5" t="n">
-        <v>88.33274968960677</v>
+        <v>112.581917984503</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>70.96366930607222</v>
+        <v>53.21268906558563</v>
       </c>
       <c r="C6" t="n">
-        <v>145.3487293614446</v>
+        <v>176.9462792226282</v>
       </c>
       <c r="D6" t="n">
-        <v>60.61899374642356</v>
+        <v>73.49952362614172</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>59.28774385946488</v>
+        <v>42.93869934064274</v>
       </c>
       <c r="C7" t="n">
-        <v>146.7221943996858</v>
+        <v>193.4936367777081</v>
       </c>
       <c r="D7" t="n">
-        <v>44.97484407925062</v>
+        <v>49.40645321622073</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>38.46978379091126</v>
+        <v>27.28767743954009</v>
       </c>
       <c r="C8" t="n">
-        <v>128.9280172602124</v>
+        <v>164.8108958504333</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.63593583264045</v>
+        <v>14.08906130364597</v>
       </c>
       <c r="C9" t="n">
-        <v>91.63436721898876</v>
+        <v>110.0499906552504</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>55.23312584092555</v>
+        <v>61.21196935978863</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>39.27088991757665</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.032400260645677</v>
+        <v>7.973237032986114</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4455035838781</v>
+        <v>107.6386999453125</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0445503583878</v>
+        <v>9.966546291232641</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.441066761114076</v>
+        <v>6.949791998363171</v>
       </c>
       <c r="C2" t="n">
-        <v>9.736973730719866</v>
+        <v>12.31798844518473</v>
       </c>
       <c r="D2" t="n">
-        <v>23.72884201164541</v>
+        <v>24.71942544523043</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.52115346670159</v>
+        <v>21.83406894244906</v>
       </c>
       <c r="C3" t="n">
-        <v>55.36566178099887</v>
+        <v>70.81837064584367</v>
       </c>
       <c r="D3" t="n">
-        <v>82.03483816686348</v>
+        <v>95.04790398665494</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.9495963763807</v>
+        <v>23.38130332434203</v>
       </c>
       <c r="C4" t="n">
-        <v>100.5447093827328</v>
+        <v>102.510168286635</v>
       </c>
       <c r="D4" t="n">
-        <v>101.5912524354599</v>
+        <v>127.7548287536374</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.98167525545136</v>
+        <v>29.96784867213389</v>
       </c>
       <c r="C5" t="n">
-        <v>86.83558444063038</v>
+        <v>105.7342277473815</v>
       </c>
       <c r="D5" t="n">
-        <v>59.96024103687396</v>
+        <v>74.17103905584653</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.79001346894498</v>
+        <v>26.64659618866693</v>
       </c>
       <c r="C6" t="n">
-        <v>96.64422575376028</v>
+        <v>127.4367424974615</v>
       </c>
       <c r="D6" t="n">
-        <v>29.58496706747763</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>18.08575620763474</v>
       </c>
       <c r="C7" t="n">
-        <v>90.66832747800993</v>
+        <v>115.8805902707723</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>28.38625312059227</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>67.5098808825319</v>
+        <v>81.11199532487147</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.45319189093031</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>46.70468353413349</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>27.8983245115816</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.244496236086461</v>
+        <v>4.156719779780995</v>
       </c>
       <c r="C2" t="n">
-        <v>4.526838664282042</v>
+        <v>6.133959656134071</v>
       </c>
       <c r="D2" t="n">
-        <v>16.467835991036</v>
+        <v>17.12364345747287</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.10529335072844</v>
+        <v>23.21342446691583</v>
       </c>
       <c r="C3" t="n">
-        <v>47.50186266998193</v>
+        <v>60.85363144773854</v>
       </c>
       <c r="D3" t="n">
-        <v>82.28518383144642</v>
+        <v>93.37893288943536</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.00211203079129</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="C4" t="n">
-        <v>121.3479432357227</v>
+        <v>139.3689040948772</v>
       </c>
       <c r="D4" t="n">
-        <v>117.6084662302467</v>
+        <v>143.5040254251647</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.8167826988669</v>
+        <v>33.15852871093603</v>
       </c>
       <c r="C5" t="n">
-        <v>133.1495323884737</v>
+        <v>144.5623494503429</v>
       </c>
       <c r="D5" t="n">
-        <v>76.18362184955249</v>
+        <v>93.09422605520381</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.59254331167113</v>
+        <v>31.51704654943536</v>
       </c>
       <c r="C6" t="n">
-        <v>117.3738285289317</v>
+        <v>149.0116300459894</v>
       </c>
       <c r="D6" t="n">
-        <v>36.66925850132262</v>
+        <v>40.77492740048278</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.95464398362217</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="C7" t="n">
-        <v>113.1856928226148</v>
+        <v>144.805822880996</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>87.37063693944488</v>
+        <v>104.7279363505285</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>47.48124596819272</v>
+        <v>50.80937068558941</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
         <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.303802008968769</v>
+        <v>4.287292224445821</v>
       </c>
       <c r="C2" t="n">
-        <v>7.816675221213104</v>
+        <v>7.709664721450202</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0068154806675</v>
+        <v>20.78556239431347</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.15099352447153</v>
+        <v>18.87900835266616</v>
       </c>
       <c r="C3" t="n">
-        <v>31.75953823238432</v>
+        <v>41.81263472387165</v>
       </c>
       <c r="D3" t="n">
-        <v>76.7628529950581</v>
+        <v>86.94357668809754</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.16199803786328</v>
+        <v>36.59071868498287</v>
       </c>
       <c r="C4" t="n">
-        <v>119.8674676977186</v>
+        <v>145.3290944073596</v>
       </c>
       <c r="D4" t="n">
-        <v>129.74581309785</v>
+        <v>153.0122519407951</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.33344403320799</v>
+        <v>38.8772090881737</v>
       </c>
       <c r="C5" t="n">
-        <v>178.7762569433442</v>
+        <v>198.6321042617359</v>
       </c>
       <c r="D5" t="n">
-        <v>96.89849840916021</v>
+        <v>118.349685746953</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.80388110999145</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C6" t="n">
-        <v>160.8053652171063</v>
+        <v>184.8356037739555</v>
       </c>
       <c r="D6" t="n">
-        <v>48.86551023118075</v>
+        <v>56.31206656789281</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.85400699617026</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>140.7335334037803</v>
+        <v>177.8033449684356</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.77315952705676</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>116.4107340310655</v>
+        <v>142.7804773671348</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>73.44061876388687</v>
+        <v>82.42655550085793</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.746349239405828</v>
+        <v>2.622248118043231</v>
       </c>
       <c r="C2" t="n">
-        <v>3.642283982755667</v>
+        <v>3.797400120026662</v>
       </c>
       <c r="D2" t="n">
-        <v>11.8516582856675</v>
+        <v>14.67909167389831</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.21128104505809</v>
+        <v>18.77101610519901</v>
       </c>
       <c r="C3" t="n">
-        <v>33.25179474283947</v>
+        <v>39.72151211382595</v>
       </c>
       <c r="D3" t="n">
-        <v>75.89891501532091</v>
+        <v>86.76195336281188</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.96078081622169</v>
+        <v>39.88350048502667</v>
       </c>
       <c r="C4" t="n">
-        <v>116.7023130992269</v>
+        <v>145.35461984767</v>
       </c>
       <c r="D4" t="n">
-        <v>138.5393272847886</v>
+        <v>162.4949530161151</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.76326960121884</v>
+        <v>40.15348110369455</v>
       </c>
       <c r="C5" t="n">
-        <v>217.4816601832747</v>
+        <v>244.7742463613361</v>
       </c>
       <c r="D5" t="n">
-        <v>102.4699166307609</v>
+        <v>121.0249482410256</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.7070068824405</v>
+        <v>29.74597369097411</v>
       </c>
       <c r="C6" t="n">
-        <v>192.765179981157</v>
+        <v>216.9966768173768</v>
       </c>
       <c r="D6" t="n">
-        <v>48.1409804254466</v>
+        <v>54.54099370943156</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.07902284242525</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>148.8781123582118</v>
+        <v>184.5106452838498</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>34.2551408965797</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>89.45685081096936</v>
+        <v>101.3065456012284</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.39218466454675</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.75264063625881</v>
+        <v>3.123921194913351</v>
       </c>
       <c r="C2" t="n">
-        <v>3.518583772020568</v>
+        <v>5.612651625179015</v>
       </c>
       <c r="D2" t="n">
-        <v>16.84090011864978</v>
+        <v>18.18294923035517</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.24225500323749</v>
+        <v>14.16171063376024</v>
       </c>
       <c r="C3" t="n">
-        <v>23.56194490192345</v>
+        <v>27.72946390645116</v>
       </c>
       <c r="D3" t="n">
-        <v>69.26230053461248</v>
+        <v>79.35466693426969</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.66349118828415</v>
+        <v>38.14777054391831</v>
       </c>
       <c r="C4" t="n">
-        <v>101.1573199501829</v>
+        <v>123.747334624902</v>
       </c>
       <c r="D4" t="n">
-        <v>143.3508727833023</v>
+        <v>168.7997367727881</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.48886327011525</v>
+        <v>47.88474427463818</v>
       </c>
       <c r="C5" t="n">
-        <v>218.095252498429</v>
+        <v>256.7024809679348</v>
       </c>
       <c r="D5" t="n">
-        <v>122.963899956913</v>
+        <v>143.0651842013665</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.98376192404687</v>
+        <v>38.23907308041327</v>
       </c>
       <c r="C6" t="n">
-        <v>260.5489684731738</v>
+        <v>289.8119222936585</v>
       </c>
       <c r="D6" t="n">
-        <v>63.59761628110839</v>
+        <v>71.76870242355459</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.89475737366311</v>
+        <v>15.92983824910874</v>
       </c>
       <c r="C7" t="n">
-        <v>204.3331131802971</v>
+        <v>239.5464398362217</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.759332943739289</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>134.7694161004809</v>
+        <v>155.1308634865597</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>60.34999487545991</v>
+        <v>63.78905708343648</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>14.56913593102267</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.60978849752428</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.21334235145782</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.325179474283947</v>
+        <v>2.072469403665017</v>
       </c>
       <c r="C2" t="n">
-        <v>2.482839944040183</v>
+        <v>3.424335992412874</v>
       </c>
       <c r="D2" t="n">
-        <v>12.21785017935156</v>
+        <v>14.53575650907827</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.12797135891735</v>
+        <v>12.92961726493049</v>
       </c>
       <c r="C3" t="n">
-        <v>19.31097734253476</v>
+        <v>25.66288498901162</v>
       </c>
       <c r="D3" t="n">
-        <v>67.95166734944299</v>
+        <v>76.45851120674159</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.11996281302991</v>
+        <v>34.45934441906305</v>
       </c>
       <c r="C4" t="n">
-        <v>85.88034392439823</v>
+        <v>105.3945430417121</v>
       </c>
       <c r="D4" t="n">
-        <v>144.9462128027033</v>
+        <v>171.5820097666236</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.67387380687015</v>
+        <v>52.30260894374884</v>
       </c>
       <c r="C5" t="n">
-        <v>213.5546693662875</v>
+        <v>252.6282279953105</v>
       </c>
       <c r="D5" t="n">
-        <v>136.512018275519</v>
+        <v>157.4968754537946</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.08063615159783</v>
+        <v>43.55229165579701</v>
       </c>
       <c r="C6" t="n">
-        <v>300.4786111003001</v>
+        <v>338.7176841807133</v>
       </c>
       <c r="D6" t="n">
-        <v>76.5989011284489</v>
+        <v>84.81023892676923</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4992929753009</v>
+        <v>14.19312656029614</v>
       </c>
       <c r="C7" t="n">
-        <v>261.3451658613179</v>
+        <v>297.1573586168331</v>
       </c>
       <c r="D7" t="n">
-        <v>42.81892612072463</v>
+        <v>45.03473068920969</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>170.8191918004238</v>
+        <v>194.7689270455247</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>68.44843168779184</v>
+        <v>67.78280674431251</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.609305471438774</v>
+        <v>2.552544031041707</v>
       </c>
       <c r="C2" t="n">
-        <v>7.043058030266617</v>
+        <v>7.712609964562943</v>
       </c>
       <c r="D2" t="n">
-        <v>11.4805576534622</v>
+        <v>13.21628759457056</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.82439033412684</v>
+        <v>10.19544990860313</v>
       </c>
       <c r="C3" t="n">
-        <v>14.93238258159398</v>
+        <v>20.15037162966578</v>
       </c>
       <c r="D3" t="n">
-        <v>62.77785694806229</v>
+        <v>71.26015711275474</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.94280625790898</v>
+        <v>29.69884980117026</v>
       </c>
       <c r="C4" t="n">
-        <v>68.53580723346982</v>
+        <v>87.97343002985242</v>
       </c>
       <c r="D4" t="n">
-        <v>145.0993654445658</v>
+        <v>170.0121951875329</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.47752426602079</v>
+        <v>52.27806525114266</v>
       </c>
       <c r="C5" t="n">
-        <v>189.5754816900591</v>
+        <v>228.6735840116883</v>
       </c>
       <c r="D5" t="n">
-        <v>151.4591270726767</v>
+        <v>174.2111301185965</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>75.63286138747003</v>
+        <v>51.96488773348793</v>
       </c>
       <c r="C6" t="n">
-        <v>320.0006641992479</v>
+        <v>362.908929361059</v>
       </c>
       <c r="D6" t="n">
-        <v>93.98761646606842</v>
+        <v>103.6882655317311</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.52516257297658</v>
+        <v>25.63146906247572</v>
       </c>
       <c r="C7" t="n">
-        <v>328.5379422353781</v>
+        <v>367.9433315884365</v>
       </c>
       <c r="D7" t="n">
-        <v>50.72395863531995</v>
+        <v>52.87987659384594</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>236.99389580518</v>
+        <v>267.4526183294373</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>35.38218726105504</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>120.3671772791802</v>
+        <v>123.9171769777366</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>48.9695754878309</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>18.00819813899924</v>
+      </c>
+      <c r="D12" t="n">
         <v>19.96089432274615</v>
-      </c>
-      <c r="D12" t="n">
-        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>12.22766765639403</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.092546326106458</v>
+        <v>5.373105185342792</v>
       </c>
       <c r="C2" t="n">
-        <v>7.698865496703487</v>
+        <v>11.04269817736812</v>
       </c>
       <c r="D2" t="n">
-        <v>5.568472978487908</v>
+        <v>14.40812930752619</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.336960446734909</v>
+        <v>1.885937339858123</v>
       </c>
       <c r="C2" t="n">
-        <v>4.05658151394782</v>
+        <v>4.626976930115218</v>
       </c>
       <c r="D2" t="n">
-        <v>8.542186774651496</v>
+        <v>9.832203258031806</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.57114048416017</v>
+        <v>13.39594742444773</v>
       </c>
       <c r="C3" t="n">
-        <v>20.78850763742621</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="D3" t="n">
-        <v>67.23008278682157</v>
+        <v>77.13100838415066</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.74756163795088</v>
+        <v>40.29190752999335</v>
       </c>
       <c r="C4" t="n">
-        <v>100.7489129052162</v>
+        <v>127.3719471489812</v>
       </c>
       <c r="D4" t="n">
-        <v>148.4431981252305</v>
+        <v>172.7561800209027</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.93320976504477</v>
+        <v>29.25608158655496</v>
       </c>
       <c r="C5" t="n">
-        <v>276.8037652123882</v>
+        <v>320.4669943587651</v>
       </c>
       <c r="D5" t="n">
-        <v>137.1256105906733</v>
+        <v>155.3370305044516</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.51325842733861</v>
+        <v>15.8994040702771</v>
       </c>
       <c r="C6" t="n">
-        <v>275.9653526729614</v>
+        <v>302.813207140999</v>
       </c>
       <c r="D6" t="n">
-        <v>75.10958986110649</v>
+        <v>80.42280843649023</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>4.671155576806323</v>
       </c>
       <c r="C7" t="n">
-        <v>166.6644355160512</v>
+        <v>188.0439552714341</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>88.70581381722054</v>
+        <v>91.29271901791088</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.38593432542277</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>19.63593583264045</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>14.39340309196248</v>
+      </c>
+      <c r="D11" t="n">
         <v>15.99267010218054</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>9.980447161373073</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.427903130331368</v>
+        <v>6.65428593938488</v>
       </c>
       <c r="C2" t="n">
-        <v>4.662319847468102</v>
+        <v>5.664684253504096</v>
       </c>
       <c r="D2" t="n">
-        <v>8.49506288484765</v>
+        <v>15.73741569907637</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18058482431918</v>
+        <v>11.41772580039041</v>
       </c>
       <c r="C3" t="n">
-        <v>19.39933463591697</v>
+        <v>27.82272993835461</v>
       </c>
       <c r="D3" t="n">
-        <v>7.814711725804611</v>
+        <v>15.2367243699105</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39833509994489</v>
+        <v>13.39671245607351</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14422493500561</v>
+        <v>70.13572991709071</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576274717640575</v>
+        <v>1.576083818361589</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.235079669671493</v>
+        <v>4.0938879267092</v>
       </c>
       <c r="C2" t="n">
-        <v>5.611669877474768</v>
+        <v>7.693956758182253</v>
       </c>
       <c r="D2" t="n">
-        <v>25.21128104505809</v>
+        <v>25.24858745781947</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.32494279457247</v>
+        <v>18.33904711533042</v>
       </c>
       <c r="C3" t="n">
-        <v>18.6384801651257</v>
+        <v>24.23444207933251</v>
       </c>
       <c r="D3" t="n">
-        <v>13.06215320500381</v>
+        <v>24.77440331666826</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.83326712119406</v>
+        <v>13.33704256219292</v>
       </c>
       <c r="C4" t="n">
-        <v>30.09449412598173</v>
+        <v>42.94655332227672</v>
       </c>
       <c r="D4" t="n">
-        <v>19.16960567312322</v>
+        <v>23.04947260030661</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44222238753702</v>
+        <v>15.43716459080965</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15134595152234</v>
+        <v>86.12312876978018</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2509941868499</v>
+        <v>3.249929387538875</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.540984042768997</v>
+        <v>5.455571992499525</v>
       </c>
       <c r="C2" t="n">
-        <v>5.281802648847839</v>
+        <v>8.259443435828414</v>
       </c>
       <c r="D2" t="n">
-        <v>24.17161022626072</v>
+        <v>37.85128273723578</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.91751749731004</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="C3" t="n">
-        <v>20.57743188101315</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D3" t="n">
-        <v>30.19855938263188</v>
+        <v>39.22082078466008</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.18307240354219</v>
+        <v>25.92108463522854</v>
       </c>
       <c r="C4" t="n">
-        <v>39.87073776487146</v>
+        <v>52.79937328209771</v>
       </c>
       <c r="D4" t="n">
-        <v>21.41584442043992</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.78788574262046</v>
+        <v>11.8055161435679</v>
       </c>
       <c r="C5" t="n">
-        <v>33.99301425954582</v>
+        <v>47.56567627075797</v>
       </c>
       <c r="D5" t="n">
-        <v>29.35425635697964</v>
+        <v>30.92505268377453</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
         <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73479849948529</v>
+        <v>16.72506053956398</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0822708468603</v>
+        <v>102.0228692913403</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020439549845587</v>
+        <v>4.181265134890994</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.034222300928397</v>
+        <v>5.458517235612265</v>
       </c>
       <c r="C2" t="n">
-        <v>4.141011816513046</v>
+        <v>7.372925258893546</v>
       </c>
       <c r="D2" t="n">
-        <v>24.14903002906304</v>
+        <v>30.07682266730528</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.31236000086651</v>
+        <v>17.39166058073225</v>
       </c>
       <c r="C3" t="n">
-        <v>20.51852701875834</v>
+        <v>30.10038461220721</v>
       </c>
       <c r="D3" t="n">
-        <v>41.85190463204153</v>
+        <v>59.26320016685872</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.36473678655685</v>
+        <v>28.65230674844316</v>
       </c>
       <c r="C4" t="n">
-        <v>46.36696232387261</v>
+        <v>61.73327739074368</v>
       </c>
       <c r="D4" t="n">
-        <v>31.17932533917445</v>
+        <v>42.43604451606838</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.13398501832986</v>
+        <v>24.88730430265665</v>
       </c>
       <c r="C5" t="n">
-        <v>55.07604620824608</v>
+        <v>73.55744674069228</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2132855981956</v>
+        <v>34.70478134512475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.36984114706057</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>34.25415914887547</v>
+        <v>44.92084795551706</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>37.99756314516856</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.12631096314512</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
         <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05948948841752</v>
+        <v>18.03915936880288</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8166695196762</v>
+        <v>117.684039691714</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879805519397151</v>
+        <v>6.013053122934292</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.494081137143404</v>
+        <v>6.095671495668446</v>
       </c>
       <c r="C2" t="n">
-        <v>9.020297906619694</v>
+        <v>7.818638716621598</v>
       </c>
       <c r="D2" t="n">
-        <v>23.87708591498668</v>
+        <v>33.46876098547801</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.97856578142259</v>
+        <v>16.03684874887165</v>
       </c>
       <c r="C3" t="n">
-        <v>16.88606051304514</v>
+        <v>27.45457454926206</v>
       </c>
       <c r="D3" t="n">
-        <v>47.87983553611694</v>
+        <v>64.85916208106553</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.12903522207961</v>
+        <v>22.60277739487432</v>
       </c>
       <c r="C4" t="n">
-        <v>41.1214843400819</v>
+        <v>57.81512230309466</v>
       </c>
       <c r="D4" t="n">
-        <v>38.74761839121312</v>
+        <v>53.70552641311752</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.02889695624644</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="C5" t="n">
-        <v>52.71985171805373</v>
+        <v>69.90043654237292</v>
       </c>
       <c r="D5" t="n">
-        <v>27.63619787454772</v>
+        <v>33.79666471869646</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.1006623496477</v>
+        <v>11.95474179461341</v>
       </c>
       <c r="C6" t="n">
-        <v>42.10323204432872</v>
+        <v>55.42653013866219</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>30.91327171132357</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.407867265618931</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>22.69702517448201</v>
+        <v>27.48795397120644</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.058104902112478</v>
+        <v>7.045152871679845</v>
       </c>
       <c r="C21" t="n">
-        <v>66.16973345730447</v>
+        <v>66.04830817199854</v>
       </c>
       <c r="D21" t="n">
-        <v>5.293578676584358</v>
+        <v>4.403220544799903</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.369980015780806</v>
+        <v>6.022040417849935</v>
       </c>
       <c r="C2" t="n">
-        <v>8.139670215910305</v>
+        <v>7.770533079113505</v>
       </c>
       <c r="D2" t="n">
-        <v>28.54038751015903</v>
+        <v>25.22502551291755</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.00649668549801</v>
+        <v>19.1293540172491</v>
       </c>
       <c r="C3" t="n">
-        <v>28.92719610563227</v>
+        <v>29.40334374219197</v>
       </c>
       <c r="D3" t="n">
-        <v>57.31933971245002</v>
+        <v>77.30281423239386</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.18681946790993</v>
+        <v>27.74615361742335</v>
       </c>
       <c r="C4" t="n">
-        <v>41.96382387032566</v>
+        <v>64.68146574659686</v>
       </c>
       <c r="D4" t="n">
-        <v>54.47128962243003</v>
+        <v>75.23623531495431</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.44738352016284</v>
+        <v>28.49522711576368</v>
       </c>
       <c r="C5" t="n">
-        <v>67.29880512611886</v>
+        <v>92.21065312138168</v>
       </c>
       <c r="D5" t="n">
-        <v>36.22649028670731</v>
+        <v>45.77398671050754</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.94094057349173</v>
+        <v>20.97111271041612</v>
       </c>
       <c r="C6" t="n">
-        <v>67.09951034215676</v>
+        <v>87.7083581497058</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>35.17994723398021</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.77392029058275</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>45.33416373900496</v>
+        <v>57.61091878061132</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>25.70215489718149</v>
+        <v>28.70630287217673</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.281316709304303</v>
+        <v>7.260729256586084</v>
       </c>
       <c r="C21" t="n">
-        <v>75.54366085903216</v>
+        <v>75.33006603708064</v>
       </c>
       <c r="D21" t="n">
-        <v>6.371152120641265</v>
+        <v>5.445546942439563</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.954299826256905</v>
+        <v>5.052073686054086</v>
       </c>
       <c r="C2" t="n">
-        <v>7.209955139988575</v>
+        <v>5.679410469067798</v>
       </c>
       <c r="D2" t="n">
-        <v>22.37893891830604</v>
+        <v>28.63659878517521</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.74142480535137</v>
+        <v>20.19945901487813</v>
       </c>
       <c r="C3" t="n">
-        <v>30.59125846433061</v>
+        <v>29.85003894762427</v>
       </c>
       <c r="D3" t="n">
-        <v>66.85210992068656</v>
+        <v>79.28103585645118</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.8144182928309</v>
+        <v>32.67256359733385</v>
       </c>
       <c r="C4" t="n">
-        <v>59.92097112870407</v>
+        <v>69.77379108852506</v>
       </c>
       <c r="D4" t="n">
-        <v>70.96072406295946</v>
+        <v>95.15884147723484</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.84761778832605</v>
+        <v>35.39200473809752</v>
       </c>
       <c r="C5" t="n">
-        <v>73.21383504420589</v>
+        <v>106.3723637551419</v>
       </c>
       <c r="D5" t="n">
-        <v>47.27115195948392</v>
+        <v>62.41461029749098</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.09064925062275</v>
+        <v>30.47050349670826</v>
       </c>
       <c r="C6" t="n">
-        <v>88.5133912671882</v>
+        <v>119.6279212578823</v>
       </c>
       <c r="D6" t="n">
-        <v>36.95102009244145</v>
+        <v>41.21769561509809</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.15237618280328</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>74.13962312931062</v>
+        <v>94.68073034526664</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>44.72842540548468</v>
+        <v>53.65742077560942</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.491380090655796</v>
+        <v>7.462538717591947</v>
       </c>
       <c r="C21" t="n">
-        <v>85.21444853120968</v>
+        <v>83.95356057290941</v>
       </c>
       <c r="D21" t="n">
-        <v>7.491380090655796</v>
+        <v>6.529721377892954</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_39_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497613602075</v>
+        <v>10.84497643726552</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907125827491</v>
+        <v>37.78907230795544</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.82332647096458</v>
+        <v>5.088398351111218</v>
       </c>
       <c r="C2" t="n">
-        <v>13.24770352110646</v>
+        <v>9.167560062256715</v>
       </c>
       <c r="D2" t="n">
-        <v>29.67626960397258</v>
+        <v>15.42620167683013</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.52557917913731</v>
+        <v>18.49121800948867</v>
       </c>
       <c r="C3" t="n">
-        <v>25.56471021858694</v>
+        <v>31.22448573356981</v>
       </c>
       <c r="D3" t="n">
-        <v>83.02640334815275</v>
+        <v>57.80530482605219</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.82495547567036</v>
+        <v>39.168788156335</v>
       </c>
       <c r="C4" t="n">
-        <v>71.56057191025425</v>
+        <v>70.48850341721673</v>
       </c>
       <c r="D4" t="n">
-        <v>111.4313096751257</v>
+        <v>78.55454255530854</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.77336481570179</v>
+        <v>46.6330159517235</v>
       </c>
       <c r="C5" t="n">
-        <v>117.7606371244049</v>
+        <v>144.4150872947058</v>
       </c>
       <c r="D5" t="n">
-        <v>79.59519512181016</v>
+        <v>59.46936718475055</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.1246095096439</v>
+        <v>40.29190752999335</v>
       </c>
       <c r="C6" t="n">
-        <v>143.0141333207457</v>
+        <v>178.8783587045859</v>
       </c>
       <c r="D6" t="n">
-        <v>50.59633143376788</v>
+        <v>44.07556318216056</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.58965482182061</v>
+        <v>25.33203601268044</v>
       </c>
       <c r="C7" t="n">
-        <v>133.7866866485298</v>
+        <v>158.6995163914969</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>88.37201959777664</v>
+        <v>94.96445543179397</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>48.36874589283183</v>
+        <v>46.48280855297372</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -895,7 +895,7 @@
         <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
         <v>34.87658719336794</v>
@@ -909,10 +909,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -982,7 +982,7 @@
         <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.649094739076346</v>
+        <v>7.65499040932932</v>
       </c>
       <c r="C21" t="n">
-        <v>92.74527371130068</v>
+        <v>92.81675871311801</v>
       </c>
       <c r="D21" t="n">
-        <v>7.649094739076346</v>
+        <v>7.65499040932932</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.874778262212914</v>
+        <v>5.710826395603696</v>
       </c>
       <c r="C2" t="n">
-        <v>17.73625402492288</v>
+        <v>10.3878724586355</v>
       </c>
       <c r="D2" t="n">
-        <v>27.9464301490897</v>
+        <v>19.26287170502667</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18549356284042</v>
+        <v>17.59291886010284</v>
       </c>
       <c r="C3" t="n">
-        <v>38.19489443372216</v>
+        <v>33.18798114206342</v>
       </c>
       <c r="D3" t="n">
-        <v>85.94219402976579</v>
+        <v>56.48485416384024</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.32720938961722</v>
+        <v>37.06293933072559</v>
       </c>
       <c r="C4" t="n">
-        <v>67.71899314353648</v>
+        <v>73.94720057927826</v>
       </c>
       <c r="D4" t="n">
-        <v>123.0070968558999</v>
+        <v>86.42914089107219</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.60847225911733</v>
+        <v>51.51721078035138</v>
       </c>
       <c r="C5" t="n">
-        <v>122.9393562643069</v>
+        <v>136.0947755012141</v>
       </c>
       <c r="D5" t="n">
-        <v>97.85570242080085</v>
+        <v>71.71666979522951</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.53091419048183</v>
+        <v>49.95230493978197</v>
       </c>
       <c r="C6" t="n">
-        <v>163.3009678813017</v>
+        <v>202.224319111575</v>
       </c>
       <c r="D6" t="n">
-        <v>60.94100699341652</v>
+        <v>50.75733805726436</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.27321326588365</v>
+        <v>35.15344004596554</v>
       </c>
       <c r="C7" t="n">
-        <v>165.7062497567064</v>
+        <v>202.2969684416892</v>
       </c>
       <c r="D7" t="n">
-        <v>44.43586458961913</v>
+        <v>42.04040019125691</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.44489594093983</v>
+        <v>19.19316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>127.7597374921587</v>
+        <v>145.8680738969911</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>76.10311853780424</v>
+        <v>78.4328058399819</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
         <v>35.16129402759952</v>
@@ -1223,7 +1223,7 @@
         <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
         <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.819397730832087</v>
+        <v>7.825426705294982</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6747457844631</v>
+        <v>100.7523688306729</v>
       </c>
       <c r="D21" t="n">
-        <v>8.796822447186097</v>
+        <v>8.803605043456853</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.616398689546754</v>
+        <v>6.129050917612838</v>
       </c>
       <c r="C2" t="n">
-        <v>17.4976893327909</v>
+        <v>20.07870404725577</v>
       </c>
       <c r="D2" t="n">
-        <v>29.856911181554</v>
+        <v>18.50201723423539</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82853830912208</v>
+        <v>17.81381209355838</v>
       </c>
       <c r="C3" t="n">
-        <v>51.40430979436299</v>
+        <v>36.0252320073367</v>
       </c>
       <c r="D3" t="n">
-        <v>86.89448930288519</v>
+        <v>57.64822519337271</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.25964872447344</v>
+        <v>34.5486834601495</v>
       </c>
       <c r="C4" t="n">
-        <v>78.69493247701583</v>
+        <v>76.79328717388975</v>
       </c>
       <c r="D4" t="n">
-        <v>133.727781786275</v>
+        <v>92.49143296479625</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.67014243803564</v>
+        <v>52.67076433284139</v>
       </c>
       <c r="C5" t="n">
-        <v>122.1294144083032</v>
+        <v>134.4012607113884</v>
       </c>
       <c r="D5" t="n">
-        <v>112.581917984503</v>
+        <v>81.53414683769762</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.21268906558563</v>
+        <v>57.43911293236815</v>
       </c>
       <c r="C6" t="n">
-        <v>176.9462792226282</v>
+        <v>208.7048357073082</v>
       </c>
       <c r="D6" t="n">
-        <v>73.49952362614172</v>
+        <v>59.04917916733292</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.93869934064274</v>
+        <v>45.03473068920969</v>
       </c>
       <c r="C7" t="n">
-        <v>193.4936367777081</v>
+        <v>237.8696147573682</v>
       </c>
       <c r="D7" t="n">
-        <v>49.40645321622073</v>
+        <v>45.45393695892307</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.28767743954009</v>
+        <v>26.36974333606933</v>
       </c>
       <c r="C8" t="n">
-        <v>164.8108958504333</v>
+        <v>195.0192727101076</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.08906130364597</v>
+        <v>13.20156137900685</v>
       </c>
       <c r="C9" t="n">
-        <v>110.0499906552504</v>
+        <v>120.2562397886003</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>61.21196935978863</v>
+        <v>61.4966761940202</v>
       </c>
       <c r="D10" t="n">
         <v>35.58835427894688</v>
@@ -1531,10 +1531,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>39.27088991757665</v>
+        <v>38.73780091417063</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.973237032986114</v>
+        <v>7.979575870320157</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6386999453125</v>
+        <v>107.7242742493221</v>
       </c>
       <c r="D21" t="n">
-        <v>9.966546291232641</v>
+        <v>9.974469837900196</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.949791998363171</v>
+        <v>5.730461349688632</v>
       </c>
       <c r="C2" t="n">
-        <v>12.31798844518473</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D2" t="n">
-        <v>24.71942544523043</v>
+        <v>15.35453409442012</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.83406894244906</v>
+        <v>22.39857387239098</v>
       </c>
       <c r="C3" t="n">
-        <v>70.81837064584367</v>
+        <v>56.98063675448488</v>
       </c>
       <c r="D3" t="n">
-        <v>95.04790398665494</v>
+        <v>63.4994415106837</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.38130332434203</v>
+        <v>25.29571134762332</v>
       </c>
       <c r="C4" t="n">
-        <v>102.510168286635</v>
+        <v>107.6280190688736</v>
       </c>
       <c r="D4" t="n">
-        <v>127.7548287536374</v>
+        <v>89.68363453065037</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.96784867213389</v>
+        <v>32.34858685493241</v>
       </c>
       <c r="C5" t="n">
-        <v>105.7342277473815</v>
+        <v>124.7065021319511</v>
       </c>
       <c r="D5" t="n">
-        <v>74.17103905584653</v>
+        <v>57.18680377237672</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.64659618866693</v>
+        <v>27.93464917663875</v>
       </c>
       <c r="C6" t="n">
-        <v>127.4367424974615</v>
+        <v>156.659444662072</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>29.90698031447059</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.08575620763474</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>115.8805902707723</v>
+        <v>137.1403368062369</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>28.02693346083794</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>81.11199532487147</v>
+        <v>88.62236526235957</v>
       </c>
       <c r="D8" t="n">
-        <v>26.45319189093031</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>46.70468353413349</v>
+        <v>46.92655851529327</v>
       </c>
       <c r="D9" t="n">
         <v>27.17968519207294</v>
@@ -1828,10 +1828,10 @@
         <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
         <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.156719779780995</v>
+        <v>3.567671157232909</v>
       </c>
       <c r="C2" t="n">
-        <v>6.133959656134071</v>
+        <v>6.029894399483909</v>
       </c>
       <c r="D2" t="n">
-        <v>17.12364345747287</v>
+        <v>11.01520924164921</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.21342446691583</v>
+        <v>21.72116795646068</v>
       </c>
       <c r="C3" t="n">
-        <v>60.85363144773854</v>
+        <v>57.26043485019522</v>
       </c>
       <c r="D3" t="n">
-        <v>93.37893288943536</v>
+        <v>62.25262192629025</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.8092064546734</v>
+        <v>32.7491399182651</v>
       </c>
       <c r="C4" t="n">
-        <v>139.3689040948772</v>
+        <v>127.7931169141031</v>
       </c>
       <c r="D4" t="n">
-        <v>143.5040254251647</v>
+        <v>99.53645449047136</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.15852871093603</v>
+        <v>36.22649028670731</v>
       </c>
       <c r="C5" t="n">
-        <v>144.5623494503429</v>
+        <v>160.4666622591412</v>
       </c>
       <c r="D5" t="n">
-        <v>93.09422605520381</v>
+        <v>69.80226177194822</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.51704654943536</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C6" t="n">
-        <v>149.0116300459894</v>
+        <v>180.3274183160541</v>
       </c>
       <c r="D6" t="n">
-        <v>40.77492740048278</v>
+        <v>35.94472869558847</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.76825078853552</v>
+        <v>16.22927129890402</v>
       </c>
       <c r="C7" t="n">
-        <v>144.805822880996</v>
+        <v>173.6112822713017</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>30.3625112492411</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>104.7279363505285</v>
+        <v>116.2438369213436</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="C9" t="n">
         <v>50.80937068558941</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2178,10 +2178,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.287292224445821</v>
+        <v>4.289255719854315</v>
       </c>
       <c r="C2" t="n">
-        <v>7.709664721450202</v>
+        <v>6.406885517914684</v>
       </c>
       <c r="D2" t="n">
-        <v>20.78556239431347</v>
+        <v>11.99401170278328</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.87900835266616</v>
+        <v>16.95478285234242</v>
       </c>
       <c r="C3" t="n">
-        <v>41.81263472387165</v>
+        <v>40.0896675029185</v>
       </c>
       <c r="D3" t="n">
-        <v>86.94357668809754</v>
+        <v>57.08862900195202</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.59071868498287</v>
+        <v>36.82044764777662</v>
       </c>
       <c r="C4" t="n">
-        <v>145.3290944073596</v>
+        <v>135.0423419622615</v>
       </c>
       <c r="D4" t="n">
-        <v>153.0122519407951</v>
+        <v>106.6708150572329</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.8772090881737</v>
+        <v>41.94517066394498</v>
       </c>
       <c r="C5" t="n">
-        <v>198.6321042617359</v>
+        <v>195.5886863785709</v>
       </c>
       <c r="D5" t="n">
-        <v>118.349685746953</v>
+        <v>86.34471058850698</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.15227837181205</v>
+        <v>39.64788103600744</v>
       </c>
       <c r="C6" t="n">
-        <v>184.8356037739555</v>
+        <v>216.1513920440203</v>
       </c>
       <c r="D6" t="n">
-        <v>56.31206656789281</v>
+        <v>46.77242412572655</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>24.97271635292611</v>
       </c>
       <c r="C7" t="n">
-        <v>177.8033449684356</v>
+        <v>212.4776921347287</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>142.7804773671348</v>
+        <v>166.5633155025138</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>29.2069942013426</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>82.42655550085793</v>
+        <v>89.30467991681108</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>43.84485247166256</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2467,7 +2467,7 @@
         <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2509,7 +2509,7 @@
         <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.622248118043231</v>
+        <v>2.596722677732814</v>
       </c>
       <c r="C2" t="n">
-        <v>3.797400120026662</v>
+        <v>3.104286240828415</v>
       </c>
       <c r="D2" t="n">
-        <v>14.67909167389831</v>
+        <v>8.369399178704057</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.77101610519901</v>
+        <v>17.3425731955199</v>
       </c>
       <c r="C3" t="n">
-        <v>39.72151211382595</v>
+        <v>36.41793108903543</v>
       </c>
       <c r="D3" t="n">
-        <v>86.76195336281188</v>
+        <v>56.10688129770521</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.88350048502667</v>
+        <v>40.30467025014855</v>
       </c>
       <c r="C4" t="n">
-        <v>145.35461984767</v>
+        <v>135.7315288506427</v>
       </c>
       <c r="D4" t="n">
-        <v>162.4949530161151</v>
+        <v>113.0138869743716</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.15348110369455</v>
+        <v>43.17235529425349</v>
       </c>
       <c r="C5" t="n">
-        <v>244.7742463613361</v>
+        <v>241.019061392592</v>
       </c>
       <c r="D5" t="n">
-        <v>121.0249482410256</v>
+        <v>90.49259463894975</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.74597369097411</v>
+        <v>30.87302005544945</v>
       </c>
       <c r="C6" t="n">
-        <v>216.9966768173768</v>
+        <v>253.7866902863218</v>
       </c>
       <c r="D6" t="n">
-        <v>54.54099370943156</v>
+        <v>45.76613272887356</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.665486074759095</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="C7" t="n">
-        <v>184.5106452838498</v>
+        <v>220.5623844792011</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>101.3065456012284</v>
+        <v>113.1562403914873</v>
       </c>
       <c r="D8" t="n">
-        <v>30.70906818884022</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2764,7 +2764,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.53673825678252</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2806,7 +2806,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.123921194913351</v>
+        <v>3.602032326881548</v>
       </c>
       <c r="C2" t="n">
-        <v>5.612651625179015</v>
+        <v>2.997275741065512</v>
       </c>
       <c r="D2" t="n">
-        <v>18.18294923035517</v>
+        <v>15.23868786531899</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.16171063376024</v>
+        <v>13.31249886958675</v>
       </c>
       <c r="C3" t="n">
-        <v>27.72946390645116</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D3" t="n">
-        <v>79.35466693426969</v>
+        <v>50.59927667688061</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.14777054391831</v>
+        <v>37.25438013305371</v>
       </c>
       <c r="C4" t="n">
-        <v>123.747334624902</v>
+        <v>114.3794980309789</v>
       </c>
       <c r="D4" t="n">
-        <v>168.7997367727881</v>
+        <v>114.6219897139279</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.88474427463818</v>
+        <v>50.36365722786139</v>
       </c>
       <c r="C5" t="n">
-        <v>256.7024809679348</v>
+        <v>246.9586350032852</v>
       </c>
       <c r="D5" t="n">
-        <v>143.0651842013665</v>
+        <v>106.0042083660494</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.23907308041327</v>
+        <v>40.73467574460867</v>
       </c>
       <c r="C6" t="n">
-        <v>289.8119222936585</v>
+        <v>311.0647965951934</v>
       </c>
       <c r="D6" t="n">
-        <v>71.76870242355459</v>
+        <v>59.41144407019999</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.92983824910874</v>
+        <v>16.40893112878119</v>
       </c>
       <c r="C7" t="n">
-        <v>239.5464398362217</v>
+        <v>284.7608303553085</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>155.1308634865597</v>
+        <v>181.917849596934</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>63.78905708343648</v>
+        <v>69.66874408417063</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.072469403665017</v>
+        <v>2.422953334081128</v>
       </c>
       <c r="C2" t="n">
-        <v>3.424335992412874</v>
+        <v>2.284526907782328</v>
       </c>
       <c r="D2" t="n">
-        <v>14.53575650907827</v>
+        <v>11.6042578641973</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.92961726493049</v>
+        <v>12.91979978788802</v>
       </c>
       <c r="C3" t="n">
-        <v>25.66288498901162</v>
+        <v>19.25698121880119</v>
       </c>
       <c r="D3" t="n">
-        <v>76.45851120674159</v>
+        <v>50.79071747920874</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.45934441906305</v>
+        <v>33.32346232524949</v>
       </c>
       <c r="C4" t="n">
-        <v>105.3945430417121</v>
+        <v>95.80974020515048</v>
       </c>
       <c r="D4" t="n">
-        <v>171.5820097666236</v>
+        <v>114.3412098705133</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.30260894374884</v>
+        <v>54.21701696703012</v>
       </c>
       <c r="C5" t="n">
-        <v>252.6282279953105</v>
+        <v>239.8409641474958</v>
       </c>
       <c r="D5" t="n">
-        <v>157.4968754537946</v>
+        <v>116.8770641905828</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.55229165579701</v>
+        <v>47.01393406097126</v>
       </c>
       <c r="C6" t="n">
-        <v>338.7176841807133</v>
+        <v>351.3567041251868</v>
       </c>
       <c r="D6" t="n">
-        <v>84.81023892676923</v>
+        <v>68.62907326537329</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.19312656029614</v>
+        <v>14.49255961009142</v>
       </c>
       <c r="C7" t="n">
-        <v>297.1573586168331</v>
+        <v>344.2881206546097</v>
       </c>
       <c r="D7" t="n">
-        <v>45.03473068920969</v>
+        <v>41.02232782195297</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>194.7689270455247</v>
+        <v>230.4014599711627</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>67.78280674431251</v>
+        <v>76.87968097186344</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.85664913964673</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.552544031041707</v>
+        <v>2.941316121923444</v>
       </c>
       <c r="C2" t="n">
-        <v>7.712609964562943</v>
+        <v>5.677446973659304</v>
       </c>
       <c r="D2" t="n">
-        <v>13.21628759457056</v>
+        <v>13.52259287829557</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.19544990860313</v>
+        <v>10.65687132959913</v>
       </c>
       <c r="C3" t="n">
-        <v>20.15037162966578</v>
+        <v>14.5593184539802</v>
       </c>
       <c r="D3" t="n">
-        <v>71.26015711275474</v>
+        <v>48.42961425049516</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.69884980117026</v>
+        <v>29.03518835309942</v>
       </c>
       <c r="C4" t="n">
-        <v>87.97343002985242</v>
+        <v>75.3638625165064</v>
       </c>
       <c r="D4" t="n">
-        <v>170.0121951875329</v>
+        <v>113.2436159371653</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.27806525114266</v>
+        <v>53.03891972193394</v>
       </c>
       <c r="C5" t="n">
-        <v>228.6735840116883</v>
+        <v>213.481038288469</v>
       </c>
       <c r="D5" t="n">
-        <v>174.2111301185965</v>
+        <v>125.0501138284375</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.96488773348793</v>
+        <v>55.50703345041042</v>
       </c>
       <c r="C6" t="n">
-        <v>362.908929361059</v>
+        <v>363.8347174461638</v>
       </c>
       <c r="D6" t="n">
-        <v>103.6882655317311</v>
+        <v>83.07941772418209</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.63146906247572</v>
+        <v>27.60772719112455</v>
       </c>
       <c r="C7" t="n">
-        <v>367.9433315884365</v>
+        <v>407.1091745016589</v>
       </c>
       <c r="D7" t="n">
-        <v>52.87987659384594</v>
+        <v>47.72962813736718</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>267.4526183294373</v>
+        <v>315.6024344842221</v>
       </c>
       <c r="D8" t="n">
-        <v>35.38218726105504</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>123.9171769777366</v>
+        <v>146.4374875654542</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>50.53546307610457</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.22766765639403</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.373105185342792</v>
+        <v>4.32754388031994</v>
       </c>
       <c r="C2" t="n">
-        <v>11.04269817736812</v>
+        <v>9.611310024576273</v>
       </c>
       <c r="D2" t="n">
-        <v>14.40812930752619</v>
+        <v>7.667449570167589</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.885937339858123</v>
+        <v>2.150027472300514</v>
       </c>
       <c r="C2" t="n">
-        <v>4.626976930115218</v>
+        <v>3.360522391636832</v>
       </c>
       <c r="D2" t="n">
-        <v>9.832203258031806</v>
+        <v>10.05996872541707</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.39594742444773</v>
+        <v>13.84755136840126</v>
       </c>
       <c r="C3" t="n">
-        <v>26.35010838198439</v>
+        <v>19.04099672386689</v>
       </c>
       <c r="D3" t="n">
-        <v>77.13100838415066</v>
+        <v>53.62305960596078</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.29190752999335</v>
+        <v>40.31743297030376</v>
       </c>
       <c r="C4" t="n">
-        <v>127.3719471489812</v>
+        <v>111.8269539999372</v>
       </c>
       <c r="D4" t="n">
-        <v>172.7561800209027</v>
+        <v>115.6174818860341</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.25608158655496</v>
+        <v>31.75953823238432</v>
       </c>
       <c r="C5" t="n">
-        <v>320.4669943587651</v>
+        <v>311.4840028649068</v>
       </c>
       <c r="D5" t="n">
-        <v>155.3370305044516</v>
+        <v>115.3308115563941</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.8994040702771</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C6" t="n">
-        <v>302.813207140999</v>
+        <v>332.3176708967284</v>
       </c>
       <c r="D6" t="n">
-        <v>80.42280843649023</v>
+        <v>67.54227855677206</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.671155576806323</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>188.0439552714341</v>
+        <v>221.9397765082594</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>91.29271901791088</v>
+        <v>107.8989814352457</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.39340309196248</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
         <v>15.99267010218054</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>9.980447161373073</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.65428593938488</v>
+        <v>6.381360077604268</v>
       </c>
       <c r="C2" t="n">
-        <v>5.664684253504096</v>
+        <v>8.542186774651496</v>
       </c>
       <c r="D2" t="n">
-        <v>15.73741569907637</v>
+        <v>16.63080610994097</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.41772580039041</v>
+        <v>9.198975988792613</v>
       </c>
       <c r="C3" t="n">
-        <v>27.82272993835461</v>
+        <v>24.21971586376881</v>
       </c>
       <c r="D3" t="n">
-        <v>15.2367243699105</v>
+        <v>9.576948854927634</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39671245607351</v>
+        <v>13.39829276711551</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13572991709071</v>
+        <v>70.14400331019297</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576083818361589</v>
+        <v>1.576269737307707</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.0938879267092</v>
+        <v>4.919537745980767</v>
       </c>
       <c r="C2" t="n">
-        <v>7.693956758182253</v>
+        <v>12.07255151912303</v>
       </c>
       <c r="D2" t="n">
-        <v>25.24858745781947</v>
+        <v>17.68520314430204</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.33904711533042</v>
+        <v>16.85660808191773</v>
       </c>
       <c r="C3" t="n">
-        <v>24.23444207933251</v>
+        <v>29.90894380987908</v>
       </c>
       <c r="D3" t="n">
-        <v>24.77440331666826</v>
+        <v>21.23029410433728</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.33704256219292</v>
+        <v>10.82278669161684</v>
       </c>
       <c r="C4" t="n">
-        <v>42.94655332227672</v>
+        <v>37.45858365553705</v>
       </c>
       <c r="D4" t="n">
-        <v>23.04947260030661</v>
+        <v>20.08852152429823</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43716459080965</v>
+        <v>15.44035930532615</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12312876978018</v>
+        <v>86.14095191392482</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249929387538875</v>
+        <v>3.250601959016031</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.455571992499525</v>
+        <v>5.66959299202533</v>
       </c>
       <c r="C2" t="n">
-        <v>8.259443435828414</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="D2" t="n">
-        <v>37.85128273723578</v>
+        <v>18.3616273125281</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.99267010218054</v>
+        <v>16.96460032938488</v>
       </c>
       <c r="C3" t="n">
-        <v>27.61656292046278</v>
+        <v>40.54618018539327</v>
       </c>
       <c r="D3" t="n">
-        <v>39.22082078466008</v>
+        <v>30.44890504721482</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.92108463522854</v>
+        <v>23.1770998018587</v>
       </c>
       <c r="C4" t="n">
-        <v>52.79937328209771</v>
+        <v>58.75956359458009</v>
       </c>
       <c r="D4" t="n">
-        <v>30.28593492830985</v>
+        <v>26.21462719879833</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.8055161435679</v>
+        <v>9.842020735074275</v>
       </c>
       <c r="C5" t="n">
-        <v>47.56567627075797</v>
+        <v>41.72427743048944</v>
       </c>
       <c r="D5" t="n">
-        <v>30.92505268377453</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72506053956398</v>
+        <v>16.73074012281777</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0228692913403</v>
+        <v>102.0575147491884</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181265134890994</v>
+        <v>4.182685030704443</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.458517235612265</v>
+        <v>6.810383824360123</v>
       </c>
       <c r="C2" t="n">
-        <v>7.372925258893546</v>
+        <v>9.451285148784043</v>
       </c>
       <c r="D2" t="n">
-        <v>30.07682266730528</v>
+        <v>22.56547098211293</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.39166058073225</v>
+        <v>18.2359636063845</v>
       </c>
       <c r="C3" t="n">
-        <v>30.10038461220721</v>
+        <v>37.52239725631309</v>
       </c>
       <c r="D3" t="n">
-        <v>59.26320016685872</v>
+        <v>37.63038950378024</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.65230674844316</v>
+        <v>28.14179794223482</v>
       </c>
       <c r="C4" t="n">
-        <v>61.73327739074368</v>
+        <v>81.60483267240336</v>
       </c>
       <c r="D4" t="n">
-        <v>42.43604451606838</v>
+        <v>35.07195498651306</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.88730430265665</v>
+        <v>22.26112919379643</v>
       </c>
       <c r="C5" t="n">
-        <v>73.55744674069228</v>
+        <v>77.80350556155973</v>
       </c>
       <c r="D5" t="n">
-        <v>34.70478134512475</v>
+        <v>32.22586839190156</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.90819874188631</v>
+        <v>9.579894098040377</v>
       </c>
       <c r="C6" t="n">
-        <v>44.92084795551706</v>
+        <v>40.13090090649688</v>
       </c>
       <c r="D6" t="n">
         <v>37.99756314516856</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03915936880288</v>
+        <v>18.04971795442064</v>
       </c>
       <c r="C21" t="n">
-        <v>117.684039691714</v>
+        <v>117.7529218931251</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013053122934292</v>
+        <v>6.016572651473545</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.095671495668446</v>
+        <v>6.859471209572464</v>
       </c>
       <c r="C2" t="n">
-        <v>7.818638716621598</v>
+        <v>8.446957247339556</v>
       </c>
       <c r="D2" t="n">
-        <v>33.46876098547801</v>
+        <v>24.27371198750238</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.03684874887165</v>
+        <v>18.64829764216816</v>
       </c>
       <c r="C3" t="n">
-        <v>27.45457454926206</v>
+        <v>34.75877746885832</v>
       </c>
       <c r="D3" t="n">
-        <v>64.85916208106553</v>
+        <v>43.65832040785565</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.60277739487432</v>
+        <v>23.10052348092745</v>
       </c>
       <c r="C4" t="n">
-        <v>57.81512230309466</v>
+        <v>73.81957337772617</v>
       </c>
       <c r="D4" t="n">
-        <v>53.70552641311752</v>
+        <v>39.64100880207771</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.81305133003238</v>
+        <v>19.73312885536089</v>
       </c>
       <c r="C5" t="n">
-        <v>69.90043654237292</v>
+        <v>85.68203088814039</v>
       </c>
       <c r="D5" t="n">
-        <v>33.79666471869646</v>
+        <v>29.96784867213389</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.95474179461341</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="C6" t="n">
-        <v>55.42653013866219</v>
+        <v>56.11080828852221</v>
       </c>
       <c r="D6" t="n">
-        <v>30.91327171132357</v>
+        <v>30.83276839957533</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>27.48795397120644</v>
+        <v>25.09248957284423</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.39687241888974</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.16834618797849</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.045152871679845</v>
+        <v>7.050163809091345</v>
       </c>
       <c r="C21" t="n">
-        <v>66.04830817199854</v>
+        <v>66.09528571023135</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403220544799903</v>
+        <v>4.40635238068209</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.022040417849935</v>
+        <v>5.931719629059228</v>
       </c>
       <c r="C2" t="n">
-        <v>7.770533079113505</v>
+        <v>4.490513999224911</v>
       </c>
       <c r="D2" t="n">
-        <v>25.22502551291755</v>
+        <v>19.40129813132546</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1293540172491</v>
+        <v>21.89297380470387</v>
       </c>
       <c r="C3" t="n">
-        <v>29.40334374219197</v>
+        <v>33.62485887045326</v>
       </c>
       <c r="D3" t="n">
-        <v>77.30281423239386</v>
+        <v>53.50034114292993</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.74615361742335</v>
+        <v>31.31971526088175</v>
       </c>
       <c r="C4" t="n">
-        <v>64.68146574659686</v>
+        <v>82.12810419876692</v>
       </c>
       <c r="D4" t="n">
-        <v>75.23623531495431</v>
+        <v>53.32264480846126</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.49522711576368</v>
+        <v>28.397052345339</v>
       </c>
       <c r="C5" t="n">
-        <v>92.21065312138168</v>
+        <v>116.3125592606409</v>
       </c>
       <c r="D5" t="n">
-        <v>45.77398671050754</v>
+        <v>37.65002445786519</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.97111271041612</v>
+        <v>19.52205309894783</v>
       </c>
       <c r="C6" t="n">
-        <v>87.7083581497058</v>
+        <v>102.4002125437593</v>
       </c>
       <c r="D6" t="n">
-        <v>35.17994723398021</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.42027013287564</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>57.61091878061132</v>
+        <v>56.8323928511436</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>28.70630287217673</v>
+        <v>27.37112599440107</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>20.81305133003238</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.260729256586084</v>
+        <v>7.266598291290363</v>
       </c>
       <c r="C21" t="n">
-        <v>75.33006603708064</v>
+        <v>75.39095727213753</v>
       </c>
       <c r="D21" t="n">
-        <v>5.445546942439563</v>
+        <v>5.449948718467772</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.052073686054086</v>
+        <v>4.790928796724435</v>
       </c>
       <c r="C2" t="n">
-        <v>5.679410469067798</v>
+        <v>9.671196634535329</v>
       </c>
       <c r="D2" t="n">
-        <v>28.63659878517521</v>
+        <v>18.69051279345078</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.19945901487813</v>
+        <v>21.08794068722149</v>
       </c>
       <c r="C3" t="n">
-        <v>29.85003894762427</v>
+        <v>24.1166323548229</v>
       </c>
       <c r="D3" t="n">
-        <v>79.28103585645118</v>
+        <v>56.34250074672445</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.67256359733385</v>
+        <v>37.6755498981756</v>
       </c>
       <c r="C4" t="n">
-        <v>69.77379108852506</v>
+        <v>83.31503717320132</v>
       </c>
       <c r="D4" t="n">
-        <v>95.15884147723484</v>
+        <v>66.82560273267188</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.39200473809752</v>
+        <v>38.01817984695774</v>
       </c>
       <c r="C5" t="n">
-        <v>106.3723637551419</v>
+        <v>134.7448724078747</v>
       </c>
       <c r="D5" t="n">
-        <v>62.41461029749098</v>
+        <v>48.32653074154926</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.47050349670826</v>
+        <v>29.62521872335175</v>
       </c>
       <c r="C6" t="n">
-        <v>119.6279212578823</v>
+        <v>147.0392989081575</v>
       </c>
       <c r="D6" t="n">
-        <v>41.21769561509809</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>16.5287043486993</v>
       </c>
       <c r="C7" t="n">
-        <v>94.68073034526664</v>
+        <v>105.4603201378966</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>53.65742077560942</v>
+        <v>52.40569245269473</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6546,7 +6546,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.462538717591947</v>
+        <v>7.468604730164931</v>
       </c>
       <c r="C21" t="n">
-        <v>83.95356057290941</v>
+        <v>84.02180321435547</v>
       </c>
       <c r="D21" t="n">
-        <v>6.529721377892954</v>
+        <v>6.535029138894314</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_39_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_39_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497643726552</v>
+        <v>10.84497631832189</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907230795544</v>
+        <v>37.78907189349906</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.088398351111218</v>
+        <v>1.019054117008189</v>
       </c>
       <c r="C2" t="n">
-        <v>9.167560062256715</v>
+        <v>2.765583282863265</v>
       </c>
       <c r="D2" t="n">
-        <v>15.42620167683013</v>
+        <v>20.31726873938774</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.49121800948867</v>
+        <v>8.330129270534187</v>
       </c>
       <c r="C3" t="n">
-        <v>31.22448573356981</v>
+        <v>33.11435006424491</v>
       </c>
       <c r="D3" t="n">
-        <v>57.80530482605219</v>
+        <v>84.24377050141879</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.168788156335</v>
+        <v>14.86856898081794</v>
       </c>
       <c r="C4" t="n">
-        <v>70.48850341721673</v>
+        <v>102.4208292455485</v>
       </c>
       <c r="D4" t="n">
-        <v>78.55454255530854</v>
+        <v>92.67011104696917</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.6330159517235</v>
+        <v>15.48707003449344</v>
       </c>
       <c r="C5" t="n">
-        <v>144.4150872947058</v>
+        <v>90.3698761759189</v>
       </c>
       <c r="D5" t="n">
-        <v>59.46936718475055</v>
+        <v>56.30323083855459</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.29190752999335</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>178.8783587045859</v>
+        <v>54.37998708593508</v>
       </c>
       <c r="D6" t="n">
-        <v>44.07556318216056</v>
+        <v>30.59125846433062</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.33203601268044</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>158.6995163914969</v>
+        <v>35.09355343600648</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>94.96445543179397</v>
+        <v>28.70630287217673</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>46.48280855297372</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.65499040932932</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.81675871311801</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.65499040932932</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.710826395603696</v>
+        <v>0.9002626447943252</v>
       </c>
       <c r="C2" t="n">
-        <v>10.3878724586355</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="D2" t="n">
-        <v>19.26287170502667</v>
+        <v>18.72781920621216</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.59291886010284</v>
+        <v>5.713771638716437</v>
       </c>
       <c r="C3" t="n">
-        <v>33.18798114206342</v>
+        <v>20.08164929036851</v>
       </c>
       <c r="D3" t="n">
-        <v>56.48485416384024</v>
+        <v>81.75994880967437</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.06293933072559</v>
+        <v>15.76195939168254</v>
       </c>
       <c r="C4" t="n">
-        <v>73.94720057927826</v>
+        <v>91.3555508709827</v>
       </c>
       <c r="D4" t="n">
-        <v>86.42914089107219</v>
+        <v>112.8990224929747</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.51721078035138</v>
+        <v>19.29134238844983</v>
       </c>
       <c r="C5" t="n">
-        <v>136.0947755012141</v>
+        <v>145.6177282324082</v>
       </c>
       <c r="D5" t="n">
-        <v>71.71666979522951</v>
+        <v>75.64366061221675</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.95230493978197</v>
+        <v>15.85915241440298</v>
       </c>
       <c r="C6" t="n">
-        <v>202.224319111575</v>
+        <v>101.1524112116616</v>
       </c>
       <c r="D6" t="n">
-        <v>50.75733805726436</v>
+        <v>40.25165587411923</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.15344004596554</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>202.2969684416892</v>
+        <v>57.3713723407751</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04040019125691</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.19316761802514</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>145.8680738969911</v>
+        <v>38.05254101660637</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>78.4328058399819</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.825426705294982</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7523688306729</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.803605043456853</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.129050917612838</v>
+        <v>0.4702571503342222</v>
       </c>
       <c r="C2" t="n">
-        <v>20.07870404725577</v>
+        <v>3.474405125329462</v>
       </c>
       <c r="D2" t="n">
-        <v>18.50201723423539</v>
+        <v>12.61349450416302</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.81381209355838</v>
+        <v>5.203262832508095</v>
       </c>
       <c r="C3" t="n">
-        <v>36.0252320073367</v>
+        <v>27.88654353913065</v>
       </c>
       <c r="D3" t="n">
-        <v>57.64822519337271</v>
+        <v>81.05309046261667</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.5486834601495</v>
+        <v>17.21690948937631</v>
       </c>
       <c r="C4" t="n">
-        <v>76.79328717388975</v>
+        <v>83.68515605770236</v>
       </c>
       <c r="D4" t="n">
-        <v>92.49143296479625</v>
+        <v>127.4485234699124</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.67076433284139</v>
+        <v>19.68404147014855</v>
       </c>
       <c r="C5" t="n">
-        <v>134.4012607113884</v>
+        <v>170.2350519163969</v>
       </c>
       <c r="D5" t="n">
-        <v>81.53414683769762</v>
+        <v>85.19115703601699</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.43911293236815</v>
+        <v>13.12203981496287</v>
       </c>
       <c r="C6" t="n">
-        <v>208.7048357073082</v>
+        <v>136.8153783161313</v>
       </c>
       <c r="D6" t="n">
-        <v>59.04917916733292</v>
+        <v>40.69442408873454</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.03473068920969</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>237.8696147573682</v>
+        <v>58.14989827024283</v>
       </c>
       <c r="D7" t="n">
-        <v>45.45393695892307</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.36974333606933</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>195.0192727101076</v>
+        <v>39.22082078466007</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.20156137900685</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>120.2562397886003</v>
+        <v>26.62499773917349</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>61.4966761940202</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.979575870320157</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7242742493221</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.974469837900196</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.730461349688632</v>
+        <v>0.9287333282174827</v>
       </c>
       <c r="C2" t="n">
-        <v>14.13520344574558</v>
+        <v>3.926009069282995</v>
       </c>
       <c r="D2" t="n">
-        <v>15.35453409442012</v>
+        <v>16.77217777935251</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.39857387239098</v>
+        <v>3.347759671481623</v>
       </c>
       <c r="C3" t="n">
-        <v>56.98063675448488</v>
+        <v>19.82639488726434</v>
       </c>
       <c r="D3" t="n">
-        <v>63.4994415106837</v>
+        <v>73.39054963097031</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.29571134762332</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="C4" t="n">
-        <v>107.6280190688736</v>
+        <v>76.8443380545106</v>
       </c>
       <c r="D4" t="n">
-        <v>89.68363453065037</v>
+        <v>137.9650048778043</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.34858685493241</v>
+        <v>22.92380889416302</v>
       </c>
       <c r="C5" t="n">
-        <v>124.7065021319511</v>
+        <v>163.6818859905495</v>
       </c>
       <c r="D5" t="n">
-        <v>57.18680377237672</v>
+        <v>108.6794708601219</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.93464917663875</v>
+        <v>19.07928488433252</v>
       </c>
       <c r="C6" t="n">
-        <v>156.659444662072</v>
+        <v>203.7136303789175</v>
       </c>
       <c r="D6" t="n">
-        <v>29.90698031447059</v>
+        <v>55.74854338565514</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>137.1403368062369</v>
+        <v>124.8036951546715</v>
       </c>
       <c r="D7" t="n">
-        <v>28.02693346083794</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>88.62236526235957</v>
+        <v>57.49605429921444</v>
       </c>
       <c r="D8" t="n">
-        <v>26.62008900065226</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>46.92655851529327</v>
+        <v>36.60937189136354</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.567671157232909</v>
+        <v>0.4938190952361456</v>
       </c>
       <c r="C2" t="n">
-        <v>6.029894399483909</v>
+        <v>2.031236000086651</v>
       </c>
       <c r="D2" t="n">
-        <v>11.01520924164921</v>
+        <v>12.8039535587869</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.72116795646068</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="C3" t="n">
-        <v>57.26043485019522</v>
+        <v>17.90216938694059</v>
       </c>
       <c r="D3" t="n">
-        <v>62.25262192629025</v>
+        <v>70.58275119682443</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.7491399182651</v>
+        <v>11.20566829627309</v>
       </c>
       <c r="C4" t="n">
-        <v>127.7931169141031</v>
+        <v>65.0643473512531</v>
       </c>
       <c r="D4" t="n">
-        <v>99.53645449047136</v>
+        <v>144.5250430375815</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.22649028670731</v>
+        <v>23.70920705756047</v>
       </c>
       <c r="C5" t="n">
-        <v>160.4666622591412</v>
+        <v>161.3993225781757</v>
       </c>
       <c r="D5" t="n">
-        <v>69.80226177194822</v>
+        <v>125.9582304548658</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.96610616090365</v>
+        <v>22.86294053649972</v>
       </c>
       <c r="C6" t="n">
-        <v>180.3274183160541</v>
+        <v>235.0696703048563</v>
       </c>
       <c r="D6" t="n">
-        <v>35.94472869558847</v>
+        <v>69.59511300635215</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22927129890402</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>173.6112822713017</v>
+        <v>185.7083774830309</v>
       </c>
       <c r="D7" t="n">
-        <v>30.3625112492411</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>116.2438369213436</v>
+        <v>87.03684272000096</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>50.80937068558941</v>
+        <v>46.70468353413349</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.289255719854315</v>
+        <v>0.6950773746067418</v>
       </c>
       <c r="C2" t="n">
-        <v>6.406885517914684</v>
+        <v>7.321874378272712</v>
       </c>
       <c r="D2" t="n">
-        <v>11.99401170278328</v>
+        <v>11.7112683639602</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.95478285234242</v>
+        <v>2.503456645829367</v>
       </c>
       <c r="C3" t="n">
-        <v>40.0896675029185</v>
+        <v>12.73326772408113</v>
       </c>
       <c r="D3" t="n">
-        <v>57.08862900195202</v>
+        <v>64.94261063592651</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.82044764777662</v>
+        <v>8.946666828801183</v>
       </c>
       <c r="C4" t="n">
-        <v>135.0423419622615</v>
+        <v>54.81588306662066</v>
       </c>
       <c r="D4" t="n">
-        <v>106.6708150572329</v>
+        <v>146.4905019414836</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.94517066394498</v>
+        <v>20.98485717827558</v>
       </c>
       <c r="C5" t="n">
-        <v>195.5886863785709</v>
+        <v>141.3225820263284</v>
       </c>
       <c r="D5" t="n">
-        <v>86.34471058850698</v>
+        <v>145.4704660767711</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.64788103600744</v>
+        <v>27.04911274740813</v>
       </c>
       <c r="C6" t="n">
-        <v>216.1513920440203</v>
+        <v>248.1917101198192</v>
       </c>
       <c r="D6" t="n">
-        <v>46.77242412572655</v>
+        <v>88.39263629956584</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.97271635292611</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>212.4776921347287</v>
+        <v>254.6977521558627</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>49.10702016642545</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>166.5633155025138</v>
+        <v>156.7998345837793</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>89.30467991681108</v>
+        <v>72.77499382040753</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>42.82187136383736</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>43.41779222031519</v>
+        <v>42.56367171762047</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.596722677732814</v>
+        <v>0.4663301595172349</v>
       </c>
       <c r="C2" t="n">
-        <v>3.104286240828415</v>
+        <v>3.807217597069131</v>
       </c>
       <c r="D2" t="n">
-        <v>8.369399178704057</v>
+        <v>8.432231031775853</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3425731955199</v>
+        <v>3.544109212330985</v>
       </c>
       <c r="C3" t="n">
-        <v>36.41793108903543</v>
+        <v>20.39580855572748</v>
       </c>
       <c r="D3" t="n">
-        <v>56.10688129770521</v>
+        <v>69.73353943265094</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.30467025014855</v>
+        <v>14.47292465600648</v>
       </c>
       <c r="C4" t="n">
-        <v>135.7315288506427</v>
+        <v>77.07406701730434</v>
       </c>
       <c r="D4" t="n">
-        <v>113.0138869743716</v>
+        <v>150.2937925477357</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.17235529425349</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="C5" t="n">
-        <v>241.019061392592</v>
+        <v>210.2658145570607</v>
       </c>
       <c r="D5" t="n">
-        <v>90.49259463894975</v>
+        <v>132.8795517698058</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.87302005544945</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="C6" t="n">
-        <v>253.7866902863218</v>
+        <v>228.548902053249</v>
       </c>
       <c r="D6" t="n">
-        <v>45.76613272887356</v>
+        <v>72.53348388516285</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>220.5623844792011</v>
+        <v>110.251248934621</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>113.1562403914873</v>
+        <v>53.57397222074844</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.50468473990763</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.602032326881548</v>
+        <v>0.259181393921158</v>
       </c>
       <c r="C2" t="n">
-        <v>2.997275741065512</v>
+        <v>2.286490403190821</v>
       </c>
       <c r="D2" t="n">
-        <v>15.23868786531899</v>
+        <v>6.216426463290803</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.31249886958675</v>
+        <v>2.557452769562941</v>
       </c>
       <c r="C3" t="n">
-        <v>24.48478774391545</v>
+        <v>17.37202562664731</v>
       </c>
       <c r="D3" t="n">
-        <v>50.59927667688061</v>
+        <v>60.76036541583509</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.25438013305371</v>
+        <v>10.00597260168349</v>
       </c>
       <c r="C4" t="n">
-        <v>114.3794980309789</v>
+        <v>61.4524975473291</v>
       </c>
       <c r="D4" t="n">
-        <v>114.6219897139279</v>
+        <v>144.8696364817721</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.36365722786139</v>
+        <v>15.31526418625024</v>
       </c>
       <c r="C5" t="n">
-        <v>246.9586350032852</v>
+        <v>159.0676717805895</v>
       </c>
       <c r="D5" t="n">
-        <v>106.0042083660494</v>
+        <v>139.972678932989</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.73467574460867</v>
+        <v>9.982410656781569</v>
       </c>
       <c r="C6" t="n">
-        <v>311.0647965951934</v>
+        <v>230.7224914704514</v>
       </c>
       <c r="D6" t="n">
-        <v>59.41144407019999</v>
+        <v>78.00770908404307</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.40893112878119</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="C7" t="n">
-        <v>284.7608303553085</v>
+        <v>149.4170918478433</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>181.917849596934</v>
+        <v>60.66709938393165</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>69.66874408417063</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>21.1890607007589</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.422953334081128</v>
+        <v>0.305323536020758</v>
       </c>
       <c r="C2" t="n">
-        <v>2.284526907782328</v>
+        <v>3.039490892348125</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6042578641973</v>
+        <v>9.418887474543899</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91979978788802</v>
+        <v>1.629701189049706</v>
       </c>
       <c r="C3" t="n">
-        <v>19.25698121880119</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="D3" t="n">
-        <v>50.79071747920874</v>
+        <v>51.635020504861</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.32346232524949</v>
+        <v>7.40237769002095</v>
       </c>
       <c r="C4" t="n">
-        <v>95.80974020515048</v>
+        <v>51.10193150145498</v>
       </c>
       <c r="D4" t="n">
-        <v>114.3412098705133</v>
+        <v>142.9807538988012</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.21701696703012</v>
+        <v>15.56070111231195</v>
       </c>
       <c r="C5" t="n">
-        <v>239.8409641474958</v>
+        <v>135.2848336452105</v>
       </c>
       <c r="D5" t="n">
-        <v>116.8770641905828</v>
+        <v>160.9820798038708</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.01393406097126</v>
+        <v>15.33588088803943</v>
       </c>
       <c r="C6" t="n">
-        <v>351.3567041251868</v>
+        <v>243.5225180384214</v>
       </c>
       <c r="D6" t="n">
-        <v>68.62907326537329</v>
+        <v>103.0844906936194</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.49255961009142</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>344.2881206546097</v>
+        <v>247.6910187906533</v>
       </c>
       <c r="D7" t="n">
-        <v>41.02232782195297</v>
+        <v>49.10702016642545</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>230.4014599711627</v>
+        <v>130.5969883574319</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>76.87968097186344</v>
+        <v>52.25155806312797</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>23.2968730217768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.941316121923444</v>
+        <v>0.2611448893296516</v>
       </c>
       <c r="C2" t="n">
-        <v>5.677446973659304</v>
+        <v>5.468334712654734</v>
       </c>
       <c r="D2" t="n">
-        <v>13.52259287829557</v>
+        <v>14.63000428868597</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.65687132959913</v>
+        <v>1.325359400733194</v>
       </c>
       <c r="C3" t="n">
-        <v>14.5593184539802</v>
+        <v>12.11476667040564</v>
       </c>
       <c r="D3" t="n">
-        <v>48.42961425049516</v>
+        <v>47.42823159216341</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.03518835309942</v>
+        <v>5.181664383014665</v>
       </c>
       <c r="C4" t="n">
-        <v>75.3638625165064</v>
+        <v>39.81968688425063</v>
       </c>
       <c r="D4" t="n">
-        <v>113.2436159371653</v>
+        <v>137.1226653475605</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.03891972193394</v>
+        <v>13.69538047424301</v>
       </c>
       <c r="C5" t="n">
-        <v>213.481038288469</v>
+        <v>113.9809084630547</v>
       </c>
       <c r="D5" t="n">
-        <v>125.0501138284375</v>
+        <v>173.131207643925</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.50703345041042</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="C6" t="n">
-        <v>363.8347174461638</v>
+        <v>230.561484846955</v>
       </c>
       <c r="D6" t="n">
-        <v>83.07941772418209</v>
+        <v>127.9197623679509</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.60772719112455</v>
+        <v>12.57618809140164</v>
       </c>
       <c r="C7" t="n">
-        <v>407.1091745016589</v>
+        <v>301.4691945338851</v>
       </c>
       <c r="D7" t="n">
-        <v>47.72962813736718</v>
+        <v>64.91708519561608</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.260024272905162</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>315.6024344842221</v>
+        <v>227.2304148864455</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>146.4374875654542</v>
+        <v>104.5031161262559</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>50.53546307610457</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.32754388031994</v>
+        <v>4.599487994396307</v>
       </c>
       <c r="C2" t="n">
-        <v>9.611310024576273</v>
+        <v>7.304202919596269</v>
       </c>
       <c r="D2" t="n">
-        <v>7.667449570167589</v>
+        <v>17.07161082914779</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.150027472300514</v>
+        <v>0.439822971502571</v>
       </c>
       <c r="C2" t="n">
-        <v>3.360522391636832</v>
+        <v>11.1428364432013</v>
       </c>
       <c r="D2" t="n">
-        <v>10.05996872541707</v>
+        <v>13.03171902617216</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.84755136840126</v>
+        <v>1.104466167277662</v>
       </c>
       <c r="C3" t="n">
-        <v>19.04099672386689</v>
+        <v>16.64553232550467</v>
       </c>
       <c r="D3" t="n">
-        <v>53.62305960596078</v>
+        <v>48.19399480147592</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.31743297030376</v>
+        <v>3.867104207028186</v>
       </c>
       <c r="C4" t="n">
-        <v>111.8269539999372</v>
+        <v>35.07195498651306</v>
       </c>
       <c r="D4" t="n">
-        <v>115.6174818860341</v>
+        <v>129.5160841350562</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.75953823238432</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C5" t="n">
-        <v>311.4840028649068</v>
+        <v>94.71410976721104</v>
       </c>
       <c r="D5" t="n">
-        <v>115.3308115563941</v>
+        <v>181.770587441297</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.10695374650067</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="C6" t="n">
-        <v>332.3176708967284</v>
+        <v>207.2557760958399</v>
       </c>
       <c r="D6" t="n">
-        <v>67.54227855677206</v>
+        <v>147.4418154668988</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.790928796724434</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="C7" t="n">
-        <v>221.9397765082594</v>
+        <v>319.2555176917245</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>82.64352174349649</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>107.8989814352457</v>
+        <v>306.5065420043754</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>42.22496875965531</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>180.8281096452199</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>77.86731916233578</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.381360077604268</v>
+        <v>3.66584592765759</v>
       </c>
       <c r="C2" t="n">
-        <v>8.542186774651496</v>
+        <v>4.688827035482766</v>
       </c>
       <c r="D2" t="n">
-        <v>16.63080610994097</v>
+        <v>24.46809803294325</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.198975988792613</v>
+        <v>7.417103905584653</v>
       </c>
       <c r="C3" t="n">
-        <v>24.21971586376881</v>
+        <v>14.42187377538564</v>
       </c>
       <c r="D3" t="n">
-        <v>9.576948854927634</v>
+        <v>14.62804079327748</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39829276711551</v>
+        <v>11.67743291947711</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14400331019297</v>
+        <v>59.94415565331585</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576269737307707</v>
+        <v>0.7784955279651409</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.919537745980767</v>
+        <v>2.756747553525043</v>
       </c>
       <c r="C2" t="n">
-        <v>12.07255151912303</v>
+        <v>4.282383485924587</v>
       </c>
       <c r="D2" t="n">
-        <v>17.68520314430204</v>
+        <v>23.44020818659684</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.85660808191773</v>
+        <v>10.82376843932109</v>
       </c>
       <c r="C3" t="n">
-        <v>29.90894380987908</v>
+        <v>17.03332266868216</v>
       </c>
       <c r="D3" t="n">
-        <v>21.23029410433728</v>
+        <v>32.48112279500572</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.82278669161684</v>
+        <v>9.240209392370978</v>
       </c>
       <c r="C4" t="n">
-        <v>37.45858365553705</v>
+        <v>23.99391389179205</v>
       </c>
       <c r="D4" t="n">
-        <v>20.08852152429823</v>
+        <v>22.02845498788993</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.080544369477244</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.84656962069702</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44035930532615</v>
+        <v>13.62773178478914</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14095191392482</v>
+        <v>73.75007789415298</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250601959016031</v>
+        <v>1.603262562916369</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.66959299202533</v>
+        <v>1.712167996206437</v>
       </c>
       <c r="C2" t="n">
-        <v>9.095892479846698</v>
+        <v>4.173409490753191</v>
       </c>
       <c r="D2" t="n">
-        <v>18.3616273125281</v>
+        <v>28.99002795870407</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.96460032938488</v>
+        <v>10.15618000043325</v>
       </c>
       <c r="C3" t="n">
-        <v>40.54618018539327</v>
+        <v>16.83206438931157</v>
       </c>
       <c r="D3" t="n">
-        <v>30.44890504721482</v>
+        <v>44.32100010822225</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.1770998018587</v>
+        <v>16.40009539944297</v>
       </c>
       <c r="C4" t="n">
-        <v>58.75956359458009</v>
+        <v>35.56970107256619</v>
       </c>
       <c r="D4" t="n">
-        <v>26.21462719879833</v>
+        <v>33.93607289269949</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.842020735074275</v>
+        <v>8.713010875190443</v>
       </c>
       <c r="C5" t="n">
-        <v>41.72427743048944</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D5" t="n">
-        <v>29.89421759431538</v>
+        <v>27.88163480060942</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73074012281777</v>
+        <v>14.83876925398335</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0575147491884</v>
+        <v>87.38386338456861</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182685030704443</v>
+        <v>2.473128208997225</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.810383824360123</v>
+        <v>1.862375394956199</v>
       </c>
       <c r="C2" t="n">
-        <v>9.451285148784043</v>
+        <v>10.32798584867644</v>
       </c>
       <c r="D2" t="n">
-        <v>22.56547098211293</v>
+        <v>24.28941995077033</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2359636063845</v>
+        <v>7.745989386507334</v>
       </c>
       <c r="C3" t="n">
-        <v>37.52239725631309</v>
+        <v>16.47863521578271</v>
       </c>
       <c r="D3" t="n">
-        <v>37.63038950378024</v>
+        <v>57.22607368054658</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.14179794223482</v>
+        <v>18.50594422505237</v>
       </c>
       <c r="C4" t="n">
-        <v>81.60483267240336</v>
+        <v>39.53890704083604</v>
       </c>
       <c r="D4" t="n">
-        <v>35.07195498651306</v>
+        <v>48.17926858591222</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.26112919379643</v>
+        <v>17.22967220953153</v>
       </c>
       <c r="C5" t="n">
-        <v>77.80350556155973</v>
+        <v>50.16730768701202</v>
       </c>
       <c r="D5" t="n">
-        <v>32.22586839190156</v>
+        <v>34.18936380039518</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.579894098040377</v>
+        <v>8.332092765942681</v>
       </c>
       <c r="C6" t="n">
-        <v>40.13090090649688</v>
+        <v>29.98748362621883</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>34.01264921363075</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04971795442064</v>
+        <v>16.08352222841945</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7529218931251</v>
+        <v>101.5801403900176</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016572651473545</v>
+        <v>3.386004679667253</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.859471209572464</v>
+        <v>1.57275982220339</v>
       </c>
       <c r="C2" t="n">
-        <v>8.446957247339556</v>
+        <v>10.15028951420777</v>
       </c>
       <c r="D2" t="n">
-        <v>24.27371198750238</v>
+        <v>26.19990098323463</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.64829764216816</v>
+        <v>6.994952392758524</v>
       </c>
       <c r="C3" t="n">
-        <v>34.75877746885832</v>
+        <v>30.34582153826891</v>
       </c>
       <c r="D3" t="n">
-        <v>43.65832040785565</v>
+        <v>62.95457153482671</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.10052348092745</v>
+        <v>16.57877348161589</v>
       </c>
       <c r="C4" t="n">
-        <v>73.81957337772617</v>
+        <v>40.5216364927871</v>
       </c>
       <c r="D4" t="n">
-        <v>39.64100880207771</v>
+        <v>64.5921267055104</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.73312885536089</v>
+        <v>22.85017781634452</v>
       </c>
       <c r="C5" t="n">
-        <v>85.68203088814039</v>
+        <v>62.75822199397737</v>
       </c>
       <c r="D5" t="n">
-        <v>29.96784867213389</v>
+        <v>43.81049130201392</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.62643715076748</v>
+        <v>15.85915241440298</v>
       </c>
       <c r="C6" t="n">
-        <v>56.11080828852221</v>
+        <v>56.23156325614456</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>37.35353665118265</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>25.09248957284423</v>
+        <v>30.9014907388726</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.050163809091345</v>
+        <v>17.35698572299195</v>
       </c>
       <c r="C21" t="n">
-        <v>66.09528571023135</v>
+        <v>115.4239550578964</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40635238068209</v>
+        <v>4.339246430747987</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.931719629059228</v>
+        <v>2.238384765682728</v>
       </c>
       <c r="C2" t="n">
-        <v>4.490513999224911</v>
+        <v>8.198575078165113</v>
       </c>
       <c r="D2" t="n">
-        <v>19.40129813132546</v>
+        <v>37.94847575995621</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.89297380470387</v>
+        <v>6.10647072041516</v>
       </c>
       <c r="C3" t="n">
-        <v>33.62485887045326</v>
+        <v>35.32328239880024</v>
       </c>
       <c r="D3" t="n">
-        <v>53.50034114292993</v>
+        <v>68.41799750896023</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.31971526088175</v>
+        <v>15.02172162268045</v>
       </c>
       <c r="C4" t="n">
-        <v>82.12810419876692</v>
+        <v>59.56361496435823</v>
       </c>
       <c r="D4" t="n">
-        <v>53.32264480846126</v>
+        <v>79.12886496229292</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.397052345339</v>
+        <v>23.90555659840983</v>
       </c>
       <c r="C5" t="n">
-        <v>116.3125592606409</v>
+        <v>69.01686360855078</v>
       </c>
       <c r="D5" t="n">
-        <v>37.65002445786519</v>
+        <v>56.35231822376693</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.52205309894783</v>
+        <v>23.30570875111504</v>
       </c>
       <c r="C6" t="n">
-        <v>102.4002125437593</v>
+        <v>78.0479607399172</v>
       </c>
       <c r="D6" t="n">
-        <v>33.89189424600839</v>
+        <v>42.46549694719579</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.402197763571703</v>
+        <v>13.41460063082842</v>
       </c>
       <c r="C7" t="n">
-        <v>56.8323928511436</v>
+        <v>55.39511421212627</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>38.86640986342697</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>27.37112599440107</v>
+        <v>33.29597338953057</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.98720588877834</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.266598291290363</v>
+        <v>18.65211870967487</v>
       </c>
       <c r="C21" t="n">
-        <v>75.39095727213753</v>
+        <v>128.7884387096598</v>
       </c>
       <c r="D21" t="n">
-        <v>5.449948718467772</v>
+        <v>5.32917677419282</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.790928796724435</v>
+        <v>1.977239876353076</v>
       </c>
       <c r="C2" t="n">
-        <v>9.671196634535329</v>
+        <v>4.984333094461056</v>
       </c>
       <c r="D2" t="n">
-        <v>18.69051279345078</v>
+        <v>29.71063077362123</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.08794068722149</v>
+        <v>9.184249773228911</v>
       </c>
       <c r="C3" t="n">
-        <v>24.1166323548229</v>
+        <v>49.25428232206248</v>
       </c>
       <c r="D3" t="n">
-        <v>56.34250074672445</v>
+        <v>77.39117152577607</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.6755498981756</v>
+        <v>11.47368541953247</v>
       </c>
       <c r="C4" t="n">
-        <v>83.31503717320132</v>
+        <v>72.18594519785947</v>
       </c>
       <c r="D4" t="n">
-        <v>66.82560273267188</v>
+        <v>73.33459001182824</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.01817984695774</v>
+        <v>13.10633185169492</v>
       </c>
       <c r="C5" t="n">
-        <v>134.7448724078747</v>
+        <v>46.6330159517235</v>
       </c>
       <c r="D5" t="n">
-        <v>48.32653074154926</v>
+        <v>42.14152020479434</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.62521872335175</v>
+        <v>8.291841110068562</v>
       </c>
       <c r="C6" t="n">
-        <v>147.0392989081575</v>
+        <v>36.46800022195202</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>25.60005313593983</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>105.4603201378966</v>
+        <v>23.41566449399068</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>52.40569245269473</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.468604730164931</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.02180321435547</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.535029138894314</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
